--- a/plans/2026_06_june_schedule.xlsx
+++ b/plans/2026_06_june_schedule.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>МПК Семёновский: 4-5×5 мин @ HR 171-175 / 8 мин R (темп ~3:45-3:55, до ретеста идти по HR)</t>
+          <t>Темповая sweet-spot: 4×5 мин @ HR 171-175 / 3-4 мин R трусцой (темп ~3:45-3:55, лактат ≤5-6 ммоль, до ретеста идти по HR)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/plans/2026_06_june_schedule.xlsx
+++ b/plans/2026_06_june_schedule.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Z1 30-45 мин или отдых (после МПК)</t>
+          <t>Z1 30-45 мин или отдых (после темповой)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Острая активация: 2×800м @ темп быстрее 5К-pace (3:15-3:20) + 20 мин разм + 15 мин зам</t>
+          <t>Острая активация: 2×600м @ темп 2.5К-pace (3:05-3:15) + 20 мин разм + 15 мин зам</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
@@ -865,7 +865,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>🏁 КОНТРОЛЬНАЯ 5К шоссе на максимум: 30 мин разм + 5К + 15 мин зам</t>
+          <t>🏁 КОНТРОЛЬНАЯ 2.5К на максимум: 30 мин разм + 2.5К (~7:50-8:10) + 15 мин зам</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -898,7 +898,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>восст. бег 30-40 мин Z1</t>
+          <t>восст. трусца 30-40 мин Z1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>вело 1.5ч Z2 (раскачка после контроля)</t>
+          <t>вело 1ч Z1-Z2 (мягкая раскачка)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -992,17 +992,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>вечер</t>
+          <t>утро</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>🏋 СТ ОМВ-НИЗ ЗАЛ 1ч 15м (статодинамика, поддерж. 3 круга — не до отказа)</t>
+          <t>бег 1ч Z2 + 🤸 кор 16м</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ст-омв</t>
+          <t>бег</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>бег 1ч Z2 шоссе + 🤸 кор 16м</t>
+          <t>Темповая на 10К-pace: 3×8 мин @ HR 175-178 (темп 3:25-3:35) / 3 мин R трусцой + 20 мин разм + 15 мин зам</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19">
@@ -1063,16 +1063,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>вело 1ч Z2 + кор 16м</t>
+          <t>Z1 45 мин или отдых (восст. после темповой)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>вело</t>
+          <t>бег</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="20">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>вечер</t>
+          <t>утро</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>🤸 СТ ОМВ-ВЕРХ ЗАЛ 1ч 15м (поддерж. 3 круга)</t>
+          <t>вело 1ч Z2 + кор 16м</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ст-омв</t>
+          <t>вело</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1129,16 +1129,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>длит. вело 2ч Z2 или роллер 1.5ч Z2 БЕЗ пояса (привыкание ОДА)</t>
+          <t>длит. бег 1.5ч Z2 шоссе (последняя длительная перед Ночным)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>вело-длит</t>
+          <t>бег-длит</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>бег 1.5ч Z2 🌲 пересеч.</t>
+          <t>лёгкий Z1 30-40 мин + 4×100м махом (нервно-мышечный звонок)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>бег-длит</t>
+          <t>бег</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="23">
@@ -1190,21 +1190,21 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>утро</t>
+          <t>вечер</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>отдых или прогулка 30 мин</t>
+          <t>🏁 Ночной забег 10К Москва (B-старт на максимум, цель 32:40-33:10, выложиться). Утром: лёгкая ходьба 20 мин. Pre-старт: Цитрулин + Гипоксен + Стимол</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>отдых</t>
+          <t>контроль</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="24">
@@ -1223,21 +1223,21 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>вечер</t>
+          <t>утро</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>🏋 СТ ОМВ-НИЗ ЗАЛ развивающая 1ч 30м (4 круга, последний до отказа)</t>
+          <t>отдых полный</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ст-омв-пик</t>
+          <t>отдых</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1261,16 +1261,16 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>роллер 1ч Z2 + кор 16м (техника, БЕЗ пояса)</t>
+          <t>лёгкий Z1 30 мин трусца или прогулка</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>вело</t>
+          <t>бег</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>бег 1ч Z2 шоссе + 5×30 сек разгон НА РАВНИНЕ</t>
+          <t>вело 1ч Z1-Z2 (восст.)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>бег</t>
+          <t>вело</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1322,21 +1322,21 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>вечер</t>
+          <t>утро</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>🤸 СТ ОМВ-ВЕРХ ЗАЛ развивающая 1ч 30м (4 круга)</t>
+          <t>отдых или 30 мин прогулка</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ст-омв-пик</t>
+          <t>отдых</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1360,16 +1360,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>длит. роллер 1.5-2ч Z2 + пояс 8 кг (первое включение, лёгкий рельеф)</t>
+          <t>🛼 первый роллер 1ч Z1-Z2 БЕЗ пояса (техника, привыкание после зимы)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>вело-длит</t>
+          <t>вело</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>бег 2ч Z2 🌲 пересеч. (макс июня)</t>
+          <t>бег 1.5ч Z2 шоссе или вело 2ч Z2</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="30">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>лёгкий бег 45 мин Z1 (разгрузка)</t>
+          <t>лёгкий бег 45 мин Z1 (мостик к июлю)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1482,7 +1482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Гипертрофия ОМВ + развитие ССС</t>
+          <t>ДВА B-старта: 12.06 (2.5К) + 22.06 (Ночной 10К Москва)</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65-70 ч/мес</t>
+          <t>55-65 ч/мес (меньше плана сезона из-за 2-х стартов)</t>
         </is>
       </c>
     </row>
@@ -1528,154 +1528,187 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LIT/MIT/HIT = 85/5/10%</t>
+          <t>LIT/MIT/HIT = 80/10/10%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ключевая дата:</t>
+          <t>Ключевая дата 1:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12.06 Пт — КОНТРОЛЬНАЯ 5К на максимум</t>
+          <t>12.06 Пт — КОНТРОЛЬНАЯ 2.5К на максимум</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Ключевая дата 2:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22.06 Пн — Ночной забег 10К (B-старт на максимум, цель 32:40-33:10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Цель веса:</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>83.2 → 81 кг к 12.06 (дефицит 400-500 ккал/день, белок 1.8-2.2 г/кг)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Структура недель:</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Нед 1 (01-07.06):</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Фаза B — раскачка + лактат-ретест + 1 МПК-сегмент (02.06)</t>
+          <t>Структура недель:</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Нед 2 (08-14.06):</t>
+          <t xml:space="preserve">  Нед 1 (01-07.06):</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Фаза C — подводка (объём −50%) + 🏁 КОНТРОЛЬНАЯ 5К 12.06</t>
+          <t>Фаза B — раскачка + лактат-ретест + 1 sweet-spot (02.06)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Нед 3 (15-21.06):</t>
+          <t xml:space="preserve">  Нед 2 (08-14.06):</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Запуск СТ ОМВ-блока (Вт/Пт, поддерж.) + аэро база</t>
+          <t>Фаза C — подводка + 🏁 2.5К 12.06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Нед 4 (22-28.06):</t>
+          <t xml:space="preserve">  Нед 3 (15-21.06):</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Пик СТ ОМВ (развивающая) + длительные с поясом 8 кг</t>
+          <t>Мост 10 дней между стартами: 1 темповая 10К-pace (17.06), 1 длит. бег (20.06)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Нед 4 (22-28.06):</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>🏁 Ночной 10К 22.06 + 5 дней восстановления + первый роллер 27.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  29-30.06:</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Разгрузка перед июльским блоком</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Лыжероллеры:</t>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Разгрузка перед июльским СТ ОМВ-блоком</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • 20.06 Сб — первый включить (БЕЗ пояса, техника)</t>
+          <t>ВАЖНО — сдвиги из-за двух стартов:</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • 24.06 Ср — короткая роллер-сессия Z2 (БЕЗ пояса)</t>
+          <t xml:space="preserve">  • Силовой блок СТ ОМВ-пик — отложен на ИЮЛЬ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • 27.06 Сб — длительная с поясом 8 кг (первое отягощение!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Тесты pending:</t>
+          <t xml:space="preserve">  • Длительные с поясом 10 кг — на ИЮЛЬ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Июнь = beg+вело база + 2 пиковых старта</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Лактат-ретест в лаборатории — дата ожидается</t>
+          <t>Лыжероллеры:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • 27.06 Сб — первый включить (БЕЗ пояса, после восст. от Ночного)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • С поясом 8 кг — июль</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Тесты pending:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Лактат-ретест в лаборатории — дата ожидается</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • После ретеста — пересборка зон во всех файлах</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>После 12.06 контрольной — план Нед 3-4 пересмотрим по результату.</t>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>После 22.06 — план июля пересматриваем по результатам обоих стартов.</t>
         </is>
       </c>
     </row>
